--- a/extenbooks/ES1403.xlsx
+++ b/extenbooks/ES1403.xlsx
@@ -825,7 +825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Study 5</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–1989</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -982,174 +982,175 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ES1403-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mohun 2005 CJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># ES1403 — Variable Capital — Mohun 2005</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: External study (Mohun 2005 CJE)</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t># ES1403 — Variable Capital — Mohun 2005</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Period**: [1948, 1989]</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Units**: ratio</t>
+          <t>**Chapter**: External study (Mohun 2005 CJE)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Period**: [1948, 1989]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Units**: ratio</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Mohun's V*, the wage bill of productive labor under Mohun's classification.</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>## Source</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mohun's V*, the wage bill of productive labor under Mohun's classification.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>`data/source/external_studies/Mohun_mohun_variable_capital_1948_1989_CORRECTED.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_ES1403_variable_capital_mohun2005.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_ES1403_variable_capital_mohun2005.py`.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>## Source</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>## Validation</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>`data/source/external_studies/Mohun_mohun_variable_capital_1948_1989_CORRECTED.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_ES1403_variable_capital_mohun2005.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_ES1403_variable_capital_mohun2005.py`.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>V03 PASS against endpoint values verified directly against the source CSV.</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>## Validation</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>## Provenance</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>V03 PASS against endpoint values verified directly against the source CSV.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>data/source/external_studies/Mohun_mohun_variable_capital_1948_1989_CORRECTED.csv</t>
+          <t>## Provenance</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  -&gt; L01_ES1403 -&gt; data/intermediate/ES1403.csv</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; P02_ES1403 -&gt; data/final/ES1403.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1158,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  -&gt; V03_ES1403 -&gt; data/intermediate/validation/ES1403.json</t>
+          <t>data/source/external_studies/Mohun_mohun_variable_capital_1948_1989_CORRECTED.csv</t>
         </is>
       </c>
     </row>
@@ -1165,53 +1166,77 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  -&gt; L01_ES1403 -&gt; data/intermediate/ES1403.csv</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  -&gt; P02_ES1403 -&gt; data/final/ES1403.csv</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t xml:space="preserve">  -&gt; V03_ES1403 -&gt; data/intermediate/validation/ES1403.json</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Mohun, Simon. 2005. 'On Measuring the Wealth of Nations: The U.S. Economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815.</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>## Citation</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mohun, Simon. 2005. 'On Measuring the Wealth of Nations: The U.S. Economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
+      <c r="B50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch).*</t>
         </is>
@@ -1228,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -1256,130 +1281,183 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Variable capital (W_p) = total wages paid to productive workers, in billions of current dollars. For each productive SIC division i: W_p^i = ec_p^i × L_p^i, where ec_p^i = 52 × (w_pn^i)_BLS × (EC^i / WS^i)_NIPA. The BLS weekly production worker wage is annualized (×52) and grossed up by the NIPA ratio of employee compensation to wages and salaries (to include employer contributions to superannuation and benefits). Total variable capital V* = sum over all productive sectors.</t>
+          <t>Equation (5): ec_p^i = 52 × (w_pn^i)_BLS × (EC^i / WS^i)_NIPA. Equation (6): W_p^i = ec_p^i × L_p^i. SM Method (Wages): (W_p^{s,j})_SM = 52 × (w_pn^s)_BLS × (EC^s / WS^s)_NIPA × (ec^{s,j} / ec^s)_NIPA × (L_p^{s,j})_SM.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mohun_2005, Section 2.2, Equations 5-6; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>st_vs_sm_wage_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Figure 1 ST-to-SM ratio for productive wages W_p: 1964: ST = 107.6% of SM; 1989: ST = 120.8% of SM; 2001: ST = 124.1% of SM. The ST method substantially overestimates variable capital. The overestimate is primarily driven by the Services sector wage approximation, where ST assumes uniform wages across all Services divisions and across production/nonproduction workers — Mohun calls this a 'drastic assumption.' Figure 3 shows W_p/W: ST starts ~0.44 (1964), declines to ~0.32 (2001); SM starts ~0.41 (1964), declines to ~0.26 (2001).</t>
+          <t>Wages: ST: 172% of benchmark (sd 3.71) — 72% OVERESTIMATE; SM: 101.5% of benchmark (sd 1.08) — 1.5% overestimate.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mohun_2005, Figs 1 and 3; full_transcription.md Section 4</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>services_wage_approximation</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Services sector wage performance 1988-2001 benchmark comparison: ST achieves 172% of benchmark (sd 3.71) — a 72% overestimate. SM achieves 101.5% of benchmark (sd 1.08) — a 1.5% overestimate. In the benchmark year 1988, ST services productive wages = $409,098 million vs benchmark $241,564 million. SM = $245,822 million. The SM method weights BLS aggregate Services production wages by the NIPA ratio of division compensation to average Services compensation: W_p^{s,j}_SM = 52 × w_pn^s_BLS × (EC^s/WS^s)_NIPA × (ec^{s,j}/ec^s)_NIPA × L_p^{s,j}_SM.</t>
+          <t>ST assumes uniform wages across all Services divisions; ST assumes uniform wages across production and non-production workers; "Drastic assumption" only justified if positive/negative variabilities cancel on aggregation; "Casual inspection of the differences in NIPA ec in Services divisions suggests this is unlikely."</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mohun_2005, Table 3; full_transcription.md Section 3.1.2</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>transportation_wage_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ST also overestimates Transportation and Public Utilities wages by using Class 1 Railroads (SIC 4011) as proxy for the entire division. By 2001 Class 1 Railroad employment was only 2.7% of division BLS employment (down from 31.7% in 1948). SM uses the division-wide BLS wage from 1964 onwards. ST overestimate: +2.3% (1964), +44% (1989), peak +50.6% (1997), +22.7% (2001).</t>
+          <t>Uses actual BLS production wage for all Services as base; Weights by NIPA ec variation across divisions; "Always likely to be much more accurate than a presumption of uniform wages."</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mohun_2005, Section 3.2; full_transcription.md</t>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>impact_on_exploitation_rate</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The overestimate of ST productive wages is partially attenuated by the ST underestimate of productive workers numbers. Net impact: ST variable capital overestimate flows through to a compressed exploitation rate. The variable capital share W_p/W is the key driver of the exploitation rate, since e = S/V = (Y - W_p)/W_p = (Y/W_p) - 1. A 24% overestimate of W_p in 2001 means ST reports systematically lower exploitation — confirmed by Fig 4 comparison showing ST e = 2.22 vs SM e = 3.00 in 2001.</t>
+          <t>Because of the variability of nominal wages both across sectors and across time, proxies constructed according to the method of equation (27) will be meaningless.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mohun_2005, Fig 4; full_transcription.md Section 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+          <t>KB: Technical/Knowledge_Base/external_papers/productive_labor/2005_Mohun_US_1964_2001/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Variable capital (W_p) = total wages paid to productive workers, in billions of current dollars. For each productive SIC division i: W_p^i = ec_p^i × L_p^i, where ec_p^i = 52 × (w_pn^i)_BLS × (EC^i / WS^i)_NIPA. The BLS weekly production worker wage is annualized (×52) and grossed up by the NIPA ratio of employee compensation to wages and salaries (to include employer contributions to superannuation and benefits). Total variable capital V* = sum over all productive sectors.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mohun_2005, Section 2.2, Equations 5-6; full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>st_vs_sm_wage_comparison</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Variable capital (wages of productive workers) under Mohun SM approximation, billions of current dollars. W_p/W declines from ~0.41 (1964) to ~0.26 (2001) under SM — steeper than ST's 0.44 to 0.32. ST overestimates by 7.6% (1964) to 24.1% (2001), primarily from services sector wage mis-approximation. Loaded from Mohun 2005 Table 2 via L15.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>Figure 1 ST-to-SM ratio for productive wages W_p: 1964: ST = 107.6% of SM; 1989: ST = 120.8% of SM; 2001: ST = 124.1% of SM. The ST method substantially overestimates variable capital. The overestimate is primarily driven by the Services sector wage approximation, where ST assumes uniform wages across all Services divisions and across production/nonproduction workers — Mohun calls this a 'drastic assumption.' Figure 3 shows W_p/W: ST starts ~0.44 (1964), declines to ~0.32 (2001); SM starts ~0.41 (1964), declines to ~0.26 (2001).</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mohun_2005, Figs 1 and 3; full_transcription.md Section 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>services_wage_approximation</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Services sector wage performance 1988-2001 benchmark comparison: ST achieves 172% of benchmark (sd 3.71) — a 72% overestimate. SM achieves 101.5% of benchmark (sd 1.08) — a 1.5% overestimate. In the benchmark year 1988, ST services productive wages = $409,098 million vs benchmark $241,564 million. SM = $245,822 million. The SM method weights BLS aggregate Services production wages by the NIPA ratio of division compensation to average Services compensation: W_p^{s,j}_SM = 52 × w_pn^s_BLS × (EC^s/WS^s)_NIPA × (ec^{s,j}/ec^s)_NIPA × L_p^{s,j}_SM.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mohun_2005, Table 3; full_transcription.md Section 3.1.2</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>transportation_wage_note</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ST also overestimates Transportation and Public Utilities wages by using Class 1 Railroads (SIC 4011) as proxy for the entire division. By 2001 Class 1 Railroad employment was only 2.7% of division BLS employment (down from 31.7% in 1948). SM uses the division-wide BLS wage from 1964 onwards. ST overestimate: +2.3% (1964), +44% (1989), peak +50.6% (1997), +22.7% (2001).</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mohun_2005, Section 3.2; full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>impact_on_exploitation_rate</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Services wage approximation has no benchmark validation pre-1988</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Transportation and Public Utilities: Mohun's SM correction is large (up to 50.6% overestimate for ST); SM uses division-wide BLS wage</t>
-        </is>
-      </c>
-    </row>
+          <t>The overestimate of ST productive wages is partially attenuated by the ST underestimate of productive workers numbers. Net impact: ST variable capital overestimate flows through to a compressed exploitation rate. The variable capital share W_p/W is the key driver of the exploitation rate, since e = S/V = (Y - W_p)/W_p = (Y/W_p) - 1. A 24% overestimate of W_p in 2001 means ST reports systematically lower exploitation — confirmed by Fig 4 comparison showing ST e = 2.22 vs SM e = 3.00 in 2001.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mohun_2005, Fig 4; full_transcription.md Section 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Agriculture and Government Enterprises overestimates in ST have small net effect due to small sector weights</t>
+          <t>Variable capital (wages of productive workers) under Mohun SM approximation, billions of current dollars. W_p/W declines from ~0.41 (1964) to ~0.26 (2001) under SM — steeper than ST's 0.44 to 0.32. ST overestimates by 7.6% (1964) to 24.1% (2001), primarily from services sector wage mis-approximation. Loaded from Mohun 2005 Table 2 via L15.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1465,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cross_references:</t>
+          <t>known_issues:</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1473,7 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ES1401</t>
+          <t>Services wage approximation has no benchmark validation pre-1988</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1481,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ES1402</t>
+          <t>Transportation and Public Utilities: Mohun's SM correction is large (up to 50.6% overestimate for ST); SM uses division-wide BLS wage</t>
         </is>
       </c>
     </row>
@@ -1411,53 +1489,85 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Agriculture and Government Enterprises overestimates in ST have small net effect due to small sector weights</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ES1401</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ES1402</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>ES1404</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
         <is>
           <t>S507</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
         <is>
           <t>S512</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Mohun_2005</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2005. 'On measuring the wealth of nations: the US economy, 1964-2001.' Cambridge Journal of Economics 29(5): 799-815. DOI: 10.1093/cje/bei043.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1474,7 +1584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1537,7 +1647,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>null — series does not extend beyond book period</t>
+          <t>null - series does not extend beyond book period</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"1948": 1112758.197}</t>
         </is>
       </c>
     </row>
@@ -1583,6 +1693,42 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>
